--- a/GitProject/PeerTreeVerification/assets/verification-table.xlsx
+++ b/GitProject/PeerTreeVerification/assets/verification-table.xlsx
@@ -557,7 +557,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>https://github.com/THEIR-USERNAME/git-project-THEIRNAME</t>
+          <t>https://github.com/THEIR-USERNAME/THEIR-REPO-NAME</t>
         </is>
       </c>
       <c r="C3" s="4" t="n"/>
@@ -570,7 +570,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>https://github.com/YOUR-USERNAME/git-project-THEIRNAME/tree/tree-review-YOURNAME</t>
+          <t>https://github.com/YOUR-USERNAME/THEIR-REPO-NAME/tree/tree-review-YOURNAME</t>
         </is>
       </c>
       <c r="C4" s="4" t="n"/>
@@ -583,7 +583,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>https://github.com/YOUR-USERNAME/git-project-THEIRNAME/commit/SHA</t>
+          <t>https://github.com/YOUR-USERNAME/THEIR-REPO-NAME/commit/SHA</t>
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
